--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_910_South_Orkney_Islands_UK.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_910_South_Orkney_Islands_UK.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R10b199d5990d4001"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R82e9c1bedcdd41b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R770dbd650a57446c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R3603b6c26ab64da0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rb302eacb02d14c77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R8109d40487034f8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rca3e16ef1efe405e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R396dc2e9ece14aca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R51ca27977a6b433e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R6b065cbf7c964519"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rd4204428c9a54934"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R5cd712928b3f4abb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ910CommercialTable" displayName="EEZ910CommercialTable" ref="A1:O6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O6"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ910CommercialTable" displayName="EEZ910CommercialTable" ref="A1:E6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E6"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ910FunctionalTable" displayName="EEZ910FunctionalTable" ref="A1:O17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O17"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ910FunctionalTable" displayName="EEZ910FunctionalTable" ref="A1:E17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E17"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ910ValidationTable" displayName="EEZ910ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ910ValidationTable" displayName="EEZ910ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -2704,7 +2658,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R867004799edf4f49"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f0b7a4486e644c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2714,20 +2668,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -2735,336 +2679,117 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>5.47492</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.57855241720427</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>378.92426528051965</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>5.47492</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>379.1519559265359</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$31,A2,'Species'!$U$2:$U$31))</x:f>
-        <x:v>2075.82662654131</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.57855241720427</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>378.92426528051965</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>2074.5800384696227</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>1.2465880716872562</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.000600886949923</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0006008869499230504</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>267059.9528983811</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.2500000000028084</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>17.782794100504223</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>267059.9528983811</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>17.78279410069709</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$31,A3,'Species'!$U$2:$U$31))</x:f>
-        <x:v>4749072.154933774</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.2500000000028084</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>17.782794100504223</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>4749072.154882267</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0.00005150679498910904</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0000000000108455</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>1.084565433190095e-11</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>8.0022515253</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.2940303978021728</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>196.80240338278517</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>8.0022515253</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>206.3694654428262</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$31,A4,'Species'!$U$2:$U$31))</x:f>
-        <x:v>1651.4203696152017</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.2940303978021728</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>196.80240338278517</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1574.8623326525985</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>76.55803696260318</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.048612526552498</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.04861252655249787</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>41.3806199999</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.082567351819964</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1209.3927250112338</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>41.3806199999</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1421.9325964813124</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$31,A5,'Species'!$U$2:$U$31))</x:f>
-        <x:v>58840.45244046433</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.082567351819964</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1209.3927250112338</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>50045.42078433342</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>8795.031656130908</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.175740987253007</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.17574098725300694</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>34.898244513200005</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.892065151413497</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>779.9471068178169</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>34.898244513200005</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>865.4593939117609</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$31,A6,'Species'!$U$2:$U$31))</x:f>
-        <x:v>30203.013544978512</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.892065151413497</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>779.9471068178169</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>27218.7848410911</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>2984.228703887413</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.109638572085784</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.10963857208578406</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G6">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O6">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e76053882bb4a5d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ebcd1ad82e54e60"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3074,20 +2799,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -3095,930 +2810,326 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.10721843780000001</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.024564403287734</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1058.1918279135211</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.10721843780000001</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1117.23235896452</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$31,A2,'Species'!$U$2:$U$31))</x:f>
-        <x:v>119.78790818778468</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.024564403287734</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1058.1918279135211</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>113.45767468161418</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>6.330233506170501</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0557937885113056</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.05579378851130567</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Krill</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>267059.9528973811</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.25</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>17.78279410038923</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>267059.9528973811</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>17.78279410038923</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$31,A3,'Species'!$U$2:$U$31))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>4749072.154833774</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.25</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>17.78279410038923</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>4749072.154833774</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.9775699999999999</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.9590729052650957</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>910.0660331196303</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.9775699999999999</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>910.8863305393267</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$31,A4,'Species'!$U$2:$U$31))</x:f>
-        <x:v>890.4551501453295</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.9590729052650957</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>910.0660331196303</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>889.6532519967569</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0.8018981485726044</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0009013603297383</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0009013603297383637</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>35.113099999999996</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.21</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1621.8100973589299</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>35.113099999999996</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1621.8100973589299</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$31,A5,'Species'!$U$2:$U$31))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>56946.78012957383</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.21</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1621.8100973589299</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>56946.78012957383</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>12.5221209088</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.6100000000000003</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>407.380277804113</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>12.5221209088</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>407.3802778041126</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$31,A6,'Species'!$U$2:$U$31))</x:f>
-        <x:v>5101.265094523631</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.6100000000000003</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>407.380277804113</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>5101.2650945236355</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>-4.547473508864641e-12</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>0.9999999999999991</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>-8.91440343640736e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>0.00022</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.29</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>194.98445997580455</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>0.00022</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>194.98445997580458</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$31,A7,'Species'!$U$2:$U$31))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>0.04289658119467701</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.29</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>194.98445997580455</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>0.04289658119467701</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>22.3761236044</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.049914383595261</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1121.7972824431668</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>22.3761236044</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1121.8095186745804</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$31,A8,'Species'!$U$2:$U$31))</x:f>
-        <x:v>25101.74845045488</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.049914383595261</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1121.7972824431668</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>25101.47465102832</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0.27379942656261846</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.000010907702849</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.000010907702848900229</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>0.0046069999</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.640811809655129</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>437.33255727666494</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>0.0046069999</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>447.5292364007221</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$31,A9,'Species'!$U$2:$U$31))</x:f>
-        <x:v>2.0617671473452033</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.640811809655129</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>437.33255727666494</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>2.01479104764034</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0.04697609970486338</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.023315618639402</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.023315618639401996</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>5.691186</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.5804441727963208</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>380.57843228395444</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>5.691186</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>382.93062930688086</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$31,A10,'Species'!$U$2:$U$31))</x:f>
-        <x:v>2179.32943648251</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.5804441727963208</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>380.57843228395444</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2165.9426457163895</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>13.386790766120612</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.006180584140857</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.00618058414085702</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>8.524656087600002</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.2880463914741114</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>194.10932147106723</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>8.524656087600002</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>196.50419010444742</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$31,A11,'Species'!$U$2:$U$31))</x:f>
-        <x:v>1675.1306404127859</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.2880463914741114</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>194.10932147106723</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1654.7152089382391</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>20.415431474546722</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0123377312085302</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.012337731208530102</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>4.4219889999</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.23</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>169.82436524617444</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>4.4219889999</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>169.82436524617444</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$31,A12,'Species'!$U$2:$U$31))</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>750.9614750335832</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.23</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>169.82436524617444</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
-        <x:v>750.9614750335832</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>0.0000010000000000000002</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>100</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>0.0000010000000000000002</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$31,A13,'Species'!$U$2:$U$31))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>0.00010000000000000002</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>0.00010000000000000002</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small bathypelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>0.011875</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.24</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>173.78008287493762</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>0.011875</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>173.78008287493762</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$31,A14,'Species'!$U$2:$U$31))</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>2.0636384841398843</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.24</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>173.78008287493762</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
-        <x:v>2.0636384841398843</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>0.00024500000000000005</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.33</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>213.79620895022325</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>0.00024500000000000005</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>213.79620895022325</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$31,A15,'Species'!$U$2:$U$31))</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>0.0523800711928047</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.33</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>213.79620895022325</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
-        <x:v>0.0523800711928047</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>0.00047</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.35</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>223.872113856834</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>0.00047</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>223.872113856834</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$31,A16,'Species'!$U$2:$U$31))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>0.10521989351271198</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.35</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>223.872113856834</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>0.10521989351271198</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>0.004655</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>199.52623149688787</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>0.004655</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>199.52623149688787</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$31,A17,'Species'!$U$2:$U$31))</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>0.9287946076180131</x:v>
       </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.3</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>199.52623149688787</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
-        <x:v>0.9287946076180131</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G17">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O17">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c67eb7007744732"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdfce41ce24e4328"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4193,7 +3304,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -4292,7 +3403,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>4841842.867915372</x:v>
+        <x:v>4829985.802878814</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -4306,7 +3417,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>4841842.867915372</x:v>
+        <x:v>4841801.612785952</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -4320,7 +3431,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-9.313225746154785e-10</x:v>
+        <x:v>-11857.065036559477</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -4334,7 +3445,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-9.313225746154785e-10</x:v>
+        <x:v>-41.25512942112982</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -4345,9 +3456,9 @@
         <x:v>EEZ_910</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -4359,47 +3470,19 @@
         <x:v>EEZ_910</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_910</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_910</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5055d0ebb9894d08"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7ba0e7ac7d24a39"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4446,7 +3529,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
